--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:59</t>
+    <t xml:space="preserve">2026-08-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:10</t>
+    <t xml:space="preserve">2026-08-17 21:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:11</t>
+    <t xml:space="preserve">2026-09-06 20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
